--- a/output/graficos_regionales_migracion/plot_migracion_saldo_se_2024_biobio.xlsx
+++ b/output/graficos_regionales_migracion/plot_migracion_saldo_se_2024_biobio.xlsx
@@ -40,7 +40,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-07 11:02</t>
+    <t xml:space="preserve">2026-09-09 19:35</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_migracion/plot_migracion_saldo_se_2024_biobio.xlsx
+++ b/output/graficos_regionales_migracion/plot_migracion_saldo_se_2024_biobio.xlsx
@@ -40,7 +40,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 19:35</t>
+    <t xml:space="preserve">2026-09-16 16:34</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_migracion/plot_migracion_saldo_se_2024_biobio.xlsx
+++ b/output/graficos_regionales_migracion/plot_migracion_saldo_se_2024_biobio.xlsx
@@ -6,29 +6,32 @@
     <workbookView xWindow="0" yWindow="0" windowWidth="13125" windowHeight="6105" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Sexo" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Resumen" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Metadata" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Edades" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Comunas" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Edades'!$A$1:$B$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Comunas'!$A$1:$D$34</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
-  <si>
-    <t xml:space="preserve">Categoría</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Saldo migratorio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hombres</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mujeres</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="56">
+  <si>
+    <t xml:space="preserve">Cambiaron de comuna dentro de la región</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cruzaron el límite</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Llegaron</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Se fueron</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Saldo de la región</t>
   </si>
   <si>
     <t xml:space="preserve">Campo</t>
@@ -40,7 +43,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-16 16:34</t>
+    <t xml:space="preserve">2026-09-30 09:55</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -58,31 +61,130 @@
     <t xml:space="preserve">Indicador</t>
   </si>
   <si>
-    <t xml:space="preserve"/>
+    <t xml:space="preserve">M_SALDOMIGR_a</t>
   </si>
   <si>
     <t xml:space="preserve">Unidad territorial</t>
   </si>
   <si>
+    <t xml:space="preserve">Región de Biobío</t>
+  </si>
+  <si>
     <t xml:space="preserve">Año</t>
   </si>
   <si>
-    <t xml:space="preserve">Tramo de edad</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0 a 4 años</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5 a 14 años</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15 a 29 años</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30 a 59 años</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60 años o más</t>
+    <t xml:space="preserve">2024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Comuna</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Con otras regiones</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Con otras comunas de la región</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Saldo de la comuna</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hualpén</t>
+  </si>
+  <si>
+    <t xml:space="preserve">San Pedro de la Paz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tomé</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Laja</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Florida</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cañete</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Negrete</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cabrero</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alto Biobío</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yumbel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Santa Bárbara</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tucapel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Los Alamos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quilaco</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arauco</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mulchén</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Contulmo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tirúa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nacimiento</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Santa Juana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Antuco</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Penco</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quilleco</t>
+  </si>
+  <si>
+    <t xml:space="preserve">San Rosendo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hualqui</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lota</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chiguayante</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Curanilahue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lebu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Los Angeles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coronel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Concepción</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Talcahuano</t>
   </si>
 </sst>
 </file>
@@ -447,8 +549,11 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
-    <col min="1" max="1" width="11.71" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="18.71" hidden="0" customWidth="1"/>
+    <col min="1" max="1" width="40.71" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="20.71" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="10.71" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="11.71" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="20.71" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -458,25 +563,35 @@
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="s">
-        <v>2</v>
+      <c r="A2" s="2" t="n">
+        <v>92101</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>1576</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" s="2" t="n">
-        <v>1495</v>
+        <v>79365</v>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>41218</v>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>38147</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>3071</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B3"/>
+  <autoFilter ref="A1:E2"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
@@ -493,58 +608,58 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>
@@ -558,60 +673,490 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
-    <col min="1" max="1" width="15.71" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="18.71" hidden="0" customWidth="1"/>
+    <col min="1" max="1" width="21.71" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="20.71" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="32.71" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="20.71" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1</v>
+        <v>20</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>301</v>
+        <v>197</v>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>2121</v>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>2318</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>733</v>
+        <v>237</v>
+      </c>
+      <c r="C3" s="2" t="n">
+        <v>857</v>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>1094</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>223</v>
+        <v>379</v>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>198</v>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>577</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="B5" s="2" t="n">
-        <v>1495</v>
+        <v>128</v>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>317</v>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>445</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>319</v>
+        <v>68</v>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>368</v>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>284</v>
+      </c>
+      <c r="C7" s="2" t="n">
+        <v>135</v>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>98</v>
+      </c>
+      <c r="C8" s="2" t="n">
+        <v>262</v>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>168</v>
+      </c>
+      <c r="C9" s="2" t="n">
+        <v>166</v>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>84</v>
+      </c>
+      <c r="C10" s="2" t="n">
+        <v>242</v>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>197</v>
+      </c>
+      <c r="C11" s="2" t="n">
+        <v>123</v>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>123</v>
+      </c>
+      <c r="C12" s="2" t="n">
+        <v>179</v>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>265</v>
+      </c>
+      <c r="C13" s="2" t="n">
+        <v>-2</v>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>136</v>
+      </c>
+      <c r="C14" s="2" t="n">
+        <v>120</v>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="C15" s="2" t="n">
+        <v>138</v>
+      </c>
+      <c r="D15" s="2" t="n">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>120</v>
+      </c>
+      <c r="C16" s="2" t="n">
+        <v>105</v>
+      </c>
+      <c r="D16" s="2" t="n">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>115</v>
+      </c>
+      <c r="C17" s="2" t="n">
+        <v>109</v>
+      </c>
+      <c r="D17" s="2" t="n">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>78</v>
+      </c>
+      <c r="C18" s="2" t="n">
+        <v>43</v>
+      </c>
+      <c r="D18" s="2" t="n">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>112</v>
+      </c>
+      <c r="C19" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="D19" s="2" t="n">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>64</v>
+      </c>
+      <c r="C20" s="2" t="n">
+        <v>43</v>
+      </c>
+      <c r="D20" s="2" t="n">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>58</v>
+      </c>
+      <c r="C21" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="D21" s="2" t="n">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B22" s="2" t="n">
+        <v>59</v>
+      </c>
+      <c r="C22" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="D22" s="2" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B23" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="C23" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="D23" s="2" t="n">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B24" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="C24" s="2" t="n">
+        <v>-4</v>
+      </c>
+      <c r="D24" s="2" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B25" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="C25" s="2" t="n">
+        <v>-27</v>
+      </c>
+      <c r="D25" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B26" s="2" t="n">
+        <v>-71</v>
+      </c>
+      <c r="C26" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="D26" s="2" t="n">
+        <v>-35</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B27" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="C27" s="2" t="n">
+        <v>-90</v>
+      </c>
+      <c r="D27" s="2" t="n">
+        <v>-62</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B28" s="2" t="n">
+        <v>-216</v>
+      </c>
+      <c r="C28" s="2" t="n">
+        <v>127</v>
+      </c>
+      <c r="D28" s="2" t="n">
+        <v>-89</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B29" s="2" t="n">
+        <v>51</v>
+      </c>
+      <c r="C29" s="2" t="n">
+        <v>-159</v>
+      </c>
+      <c r="D29" s="2" t="n">
+        <v>-108</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B30" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="C30" s="2" t="n">
+        <v>-160</v>
+      </c>
+      <c r="D30" s="2" t="n">
+        <v>-141</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B31" s="2" t="n">
+        <v>621</v>
+      </c>
+      <c r="C31" s="2" t="n">
+        <v>-1095</v>
+      </c>
+      <c r="D31" s="2" t="n">
+        <v>-474</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B32" s="2" t="n">
+        <v>-243</v>
+      </c>
+      <c r="C32" s="2" t="n">
+        <v>-523</v>
+      </c>
+      <c r="D32" s="2" t="n">
+        <v>-766</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B33" s="2" t="n">
+        <v>126</v>
+      </c>
+      <c r="C33" s="2" t="n">
+        <v>-1677</v>
+      </c>
+      <c r="D33" s="2" t="n">
+        <v>-1551</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B34" s="2" t="n">
+        <v>-415</v>
+      </c>
+      <c r="C34" s="2" t="n">
+        <v>-2034</v>
+      </c>
+      <c r="D34" s="2" t="n">
+        <v>-2449</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B6"/>
+  <autoFilter ref="A1:D34"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>

--- a/output/graficos_regionales_migracion/plot_migracion_saldo_se_2024_biobio.xlsx
+++ b/output/graficos_regionales_migracion/plot_migracion_saldo_se_2024_biobio.xlsx
@@ -43,7 +43,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-30 09:55</t>
+    <t xml:space="preserve">2026-10-05 03:50</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -124,7 +124,7 @@
     <t xml:space="preserve">Tucapel</t>
   </si>
   <si>
-    <t xml:space="preserve">Los Alamos</t>
+    <t xml:space="preserve">Los Álamos</t>
   </si>
   <si>
     <t xml:space="preserve">Quilaco</t>
@@ -175,7 +175,7 @@
     <t xml:space="preserve">Lebu</t>
   </si>
   <si>
-    <t xml:space="preserve">Los Angeles</t>
+    <t xml:space="preserve">Los Ángeles</t>
   </si>
   <si>
     <t xml:space="preserve">Coronel</t>
